--- a/artfynd/A 1963-2025 artfynd.xlsx
+++ b/artfynd/A 1963-2025 artfynd.xlsx
@@ -2982,7 +2982,7 @@
         <v>120639051</v>
       </c>
       <c r="B24" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 1963-2025 artfynd.xlsx
+++ b/artfynd/A 1963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119379737</v>
+        <v>120639467</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598035</v>
+        <v>598002</v>
       </c>
       <c r="R2" t="n">
-        <v>7043905</v>
+        <v>7043985</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119379751</v>
+        <v>119379748</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,7 +810,7 @@
         <v>598018</v>
       </c>
       <c r="R3" t="n">
-        <v>7043866</v>
+        <v>7043870</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119379739</v>
+        <v>119379749</v>
       </c>
       <c r="B4" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598011</v>
+        <v>598046</v>
       </c>
       <c r="R4" t="n">
-        <v>7043992</v>
+        <v>7043829</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119379720</v>
+        <v>120639960</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598083</v>
+        <v>597988</v>
       </c>
       <c r="R5" t="n">
-        <v>7043897</v>
+        <v>7043905</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119379748</v>
+        <v>119379720</v>
       </c>
       <c r="B6" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598018</v>
+        <v>598083</v>
       </c>
       <c r="R6" t="n">
-        <v>7043870</v>
+        <v>7043897</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119379752</v>
+        <v>120638652</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598154</v>
+        <v>598049</v>
       </c>
       <c r="R7" t="n">
-        <v>7043804</v>
+        <v>7043978</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119379744</v>
+        <v>119379750</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598008</v>
+        <v>598005</v>
       </c>
       <c r="R8" t="n">
-        <v>7043983</v>
+        <v>7043985</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1394,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119379729</v>
+        <v>120639051</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598078</v>
+        <v>598038</v>
       </c>
       <c r="R9" t="n">
-        <v>7043913</v>
+        <v>7043975</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1464,17 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119379724</v>
+        <v>119379743</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598050</v>
+        <v>597980</v>
       </c>
       <c r="R10" t="n">
-        <v>7043908</v>
+        <v>7043967</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1577,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119379733</v>
+        <v>119379744</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598042</v>
+        <v>598008</v>
       </c>
       <c r="R11" t="n">
-        <v>7043942</v>
+        <v>7043983</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1684,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119379741</v>
+        <v>119379724</v>
       </c>
       <c r="B12" t="n">
-        <v>96862</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598010</v>
+        <v>598050</v>
       </c>
       <c r="R12" t="n">
-        <v>7043951</v>
+        <v>7043908</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1795,7 +1720,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,12 +1750,7 @@
         <v>119379727</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,15 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119379734</v>
+        <v>119379728</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598006</v>
+        <v>598100</v>
       </c>
       <c r="R14" t="n">
-        <v>7043983</v>
+        <v>7043895</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2009,7 +1924,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,15 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119379723</v>
+        <v>119379729</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598028</v>
+        <v>598078</v>
       </c>
       <c r="R15" t="n">
-        <v>7043959</v>
+        <v>7043913</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2146,12 +2056,7 @@
         <v>119379731</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,15 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119379750</v>
+        <v>120638382</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,37 +2166,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598005</v>
+        <v>598083</v>
       </c>
       <c r="R17" t="n">
-        <v>7043985</v>
+        <v>7043934</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2320,12 +2220,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,15 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119379728</v>
+        <v>120638504</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,17 +2288,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598100</v>
+        <v>598028</v>
       </c>
       <c r="R18" t="n">
-        <v>7043895</v>
+        <v>7043947</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2422,17 +2322,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,15 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119379730</v>
+        <v>120638522</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,17 +2385,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598025</v>
+        <v>598039</v>
       </c>
       <c r="R19" t="n">
-        <v>7043958</v>
+        <v>7043936</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2529,12 +2419,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2566,15 +2456,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119379745</v>
+        <v>120638613</v>
       </c>
       <c r="B20" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,32 +2467,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vigdsjön, Ång</t>
+          <t>Vigdsjön, Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598140</v>
+        <v>598030</v>
       </c>
       <c r="R20" t="n">
-        <v>7043827</v>
+        <v>7043957</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2631,12 +2521,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,15 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120639264</v>
+        <v>120638857</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,13 +2593,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598004</v>
+        <v>598029</v>
       </c>
       <c r="R21" t="n">
-        <v>7043965</v>
+        <v>7043971</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2770,15 +2660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120639346</v>
+        <v>120639114</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,13 +2695,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597993</v>
+        <v>598018</v>
       </c>
       <c r="R22" t="n">
-        <v>7043984</v>
+        <v>7043971</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2877,15 +2762,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120639960</v>
+        <v>120639264</v>
       </c>
       <c r="B23" t="n">
-        <v>90675</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2893,21 +2773,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597988</v>
+        <v>598004</v>
       </c>
       <c r="R23" t="n">
-        <v>7043905</v>
+        <v>7043965</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2953,6 +2833,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2979,37 +2864,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120639051</v>
+        <v>120639346</v>
       </c>
       <c r="B24" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,13 +2899,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>598038</v>
+        <v>597993</v>
       </c>
       <c r="R24" t="n">
-        <v>7043975</v>
+        <v>7043984</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3055,6 +2935,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3084,12 +2969,7 @@
         <v>120639423</v>
       </c>
       <c r="B25" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,53 +3068,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120638652</v>
+        <v>119413932</v>
       </c>
       <c r="B26" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>101283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
+          <t>Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>598049</v>
+        <v>597993</v>
       </c>
       <c r="R26" t="n">
-        <v>7043978</v>
+        <v>7043842</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,20 +3138,26 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Kläckhål och gnaggångar på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3290,15 +3176,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120639467</v>
+        <v>119379737</v>
       </c>
       <c r="B27" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,37 +3187,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
+          <t>Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598002</v>
+        <v>598035</v>
       </c>
       <c r="R27" t="n">
-        <v>7043985</v>
+        <v>7043905</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3360,12 +3241,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3392,32 +3278,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120638857</v>
+        <v>120638144</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3432,13 +3313,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>598029</v>
+        <v>598104</v>
       </c>
       <c r="R28" t="n">
-        <v>7043971</v>
+        <v>7043873</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3472,7 +3353,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gnaggångar och kläckhål.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3499,37 +3380,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120638613</v>
+        <v>120638341</v>
       </c>
       <c r="B29" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3539,10 +3415,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>598030</v>
+        <v>598099</v>
       </c>
       <c r="R29" t="n">
-        <v>7043957</v>
+        <v>7043901</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3579,7 +3455,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,53 +3482,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120638522</v>
+        <v>119379740</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
+          <t>Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>598039</v>
+        <v>598044</v>
       </c>
       <c r="R30" t="n">
-        <v>7043936</v>
+        <v>7043831</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3676,17 +3547,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,15 +3584,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120638144</v>
+        <v>119379741</v>
       </c>
       <c r="B31" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3729,37 +3595,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
+          <t>Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>598104</v>
+        <v>598010</v>
       </c>
       <c r="R31" t="n">
-        <v>7043873</v>
+        <v>7043951</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3783,17 +3649,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3820,15 +3686,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120639114</v>
+        <v>119379745</v>
       </c>
       <c r="B32" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3836,37 +3697,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
+          <t>Vigdsjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>598018</v>
+        <v>598140</v>
       </c>
       <c r="R32" t="n">
-        <v>7043971</v>
+        <v>7043827</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3890,17 +3751,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,322 +3780,6 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>120638504</v>
-      </c>
-      <c r="B33" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>598028</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7043947</v>
-      </c>
-      <c r="S33" t="n">
-        <v>15</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>120638382</v>
-      </c>
-      <c r="B34" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>598083</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7043934</v>
-      </c>
-      <c r="S34" t="n">
-        <v>15</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>120638341</v>
-      </c>
-      <c r="B35" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Vigdsjön, Vigdsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>598099</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7043901</v>
-      </c>
-      <c r="S35" t="n">
-        <v>15</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Ådals-Liden</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1963-2025 artfynd.xlsx
+++ b/artfynd/A 1963-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379748</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639960</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379720</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379750</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639051</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379743</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379744</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379724</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379727</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379728</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379729</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379731</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638382</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638504</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638522</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2555,6 +2650,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638613</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2657,6 +2757,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638857</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639114</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2861,6 +2971,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639264</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639346</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3065,6 +3185,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120639423</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3173,6 +3298,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413932</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3275,6 +3405,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379737</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3377,6 +3512,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638144</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3479,6 +3619,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120638341</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3581,6 +3726,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379740</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3683,6 +3833,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379741</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3780,8 +3935,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119379745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>